--- a/excel_templates/wzor_import_odbiorcy.xlsx
+++ b/excel_templates/wzor_import_odbiorcy.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Szpital Przykładowy</t>
+          <t>Sklep Przykładowy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>GLS</t>
+          <t>PACZKI</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Klinika Demo</t>
+          <t>Hurtownia Demo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>GEIS</t>
+          <t>PALETY</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -678,7 +678,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Przewoźnik: np. GLS — puste = inny/dowolny.</t>
+          <t>Przewoźnik: np. PACZKI — puste = inny/dowolny.</t>
         </is>
       </c>
     </row>
